--- a/TP4/coeficientes_comparados.xlsx
+++ b/TP4/coeficientes_comparados.xlsx
@@ -1,43 +1,119 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Maestria\Programacion\BigDataUBA-Grupo1\TP4\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7570E8FB-7879-415F-AC46-47554412ECDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Logit_sin_penalidad</t>
+  </si>
+  <si>
+    <t>LASSO_(λ_opt)</t>
+  </si>
+  <si>
+    <t>Ridge_(λ_opt)</t>
+  </si>
+  <si>
+    <t>educ</t>
+  </si>
+  <si>
+    <t>CH06</t>
+  </si>
+  <si>
+    <t>edad2</t>
+  </si>
+  <si>
+    <t>horastrab</t>
+  </si>
+  <si>
+    <t>CH04</t>
+  </si>
+  <si>
+    <t>IX_TOT</t>
+  </si>
+  <si>
+    <t>CH07</t>
+  </si>
+  <si>
+    <t>CH08</t>
+  </si>
+  <si>
+    <t>ESTADO</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="172" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -46,94 +122,131 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Entrada" xfId="1" builtinId="20"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D841E81-D5ED-8D69-EFE2-6A140919E741}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5000625" y="0"/>
+          <a:ext cx="3790950" cy="1914525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -420,208 +533,156 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Logit_sin_penalidad</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LASSO_(λ_opt)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Ridge_(λ_opt)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>educ</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.2674712948077856</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.2678429267518629</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3">
+        <v>-0.26747129480778559</v>
+      </c>
+      <c r="C2" s="3">
+        <v>-0.26784292675186289</v>
+      </c>
+      <c r="D2" s="3">
         <v>-0.2644778012907319</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CH06</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.3357418794624116</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-0.3197985503159331</v>
-      </c>
-      <c r="E3" t="n">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="3">
+        <v>-0.33574187946241157</v>
+      </c>
+      <c r="C3" s="3">
+        <v>-0.31979855031593313</v>
+      </c>
+      <c r="D3" s="3">
         <v>-0.1916526710590728</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>edad2</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.2987889723351098</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2845839026376539</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.1566181986968737</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>horastrab</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.2377976524469811</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-0.2380979889962272</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.2337632746610543</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CH04</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.6783330399313013</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.6791819266380447</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.677548417274111</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>IX_TOT</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.240209782847472</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.2416834625792618</v>
-      </c>
-      <c r="E7" t="n">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.29878897233510981</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.28458390263765387</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.15661819869687371</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3">
+        <v>-0.23779765244698109</v>
+      </c>
+      <c r="C5" s="3">
+        <v>-0.23809798899622719</v>
+      </c>
+      <c r="D5" s="3">
+        <v>-0.23376327466105429</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.67833303993130134</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.67918192663804466</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.67754841727411097</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.24020978284747199</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.24168346257926179</v>
+      </c>
+      <c r="D7" s="3">
         <v>0.2370293383296844</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CH07</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.03635745172596837</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.03730361117824327</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.03752849576065551</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CH08</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.5118058638438951</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.512293619670203</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.5114767707650669</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ESTADO</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.0183005946729256</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.01865545621593882</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.01338558166972412</v>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="3">
+        <v>3.6357451725968368E-2</v>
+      </c>
+      <c r="C8" s="3">
+        <v>3.7303611178243268E-2</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3.7528495760655513E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.51180586384389515</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.51229361967020304</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.51147677076506692</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="3">
+        <v>-1.8300594672925601E-2</v>
+      </c>
+      <c r="C10" s="3">
+        <v>-1.865545621593882E-2</v>
+      </c>
+      <c r="D10" s="3">
+        <v>-1.338558166972412E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/TP4/coeficientes_comparados.xlsx
+++ b/TP4/coeficientes_comparados.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.2674712948077856</v>
+        <v>-0.2674712948078108</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2678429267518629</v>
+        <v>-0.2677980367466836</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2644778012907319</v>
+        <v>-0.2644778012909151</v>
       </c>
     </row>
     <row r="3">
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.3357418794624116</v>
+        <v>-0.3357418794624388</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3197985503159331</v>
+        <v>-0.317248377097728</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1916526710590728</v>
+        <v>-0.1916526710523312</v>
       </c>
     </row>
     <row r="4">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2987889723351098</v>
+        <v>0.2987889723351313</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2845839026376539</v>
+        <v>0.2820729688634421</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1566181986968737</v>
+        <v>0.156618198693959</v>
       </c>
     </row>
     <row r="5">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.2377976524469811</v>
+        <v>-0.2377976524469907</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2380979889962272</v>
+        <v>-0.2379799976013406</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2337632746610543</v>
+        <v>-0.2337632746645101</v>
       </c>
     </row>
     <row r="6">
@@ -536,13 +536,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6783330399313013</v>
+        <v>0.6783330399313007</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6791819266380447</v>
+        <v>0.6792264030024556</v>
       </c>
       <c r="E6" t="n">
-        <v>0.677548417274111</v>
+        <v>0.677548417276601</v>
       </c>
     </row>
     <row r="7">
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.240209782847472</v>
+        <v>0.2402097828474914</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2416834625792618</v>
+        <v>0.2416847748220056</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2370293383296844</v>
+        <v>0.2370293383284964</v>
       </c>
     </row>
     <row r="8">
@@ -574,13 +574,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03635745172596837</v>
+        <v>0.03635745172597279</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03730361117824327</v>
+        <v>0.03731824384443799</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03752849576065551</v>
+        <v>0.03752849576228024</v>
       </c>
     </row>
     <row r="9">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.5118058638438951</v>
+        <v>0.5118058638438978</v>
       </c>
       <c r="D9" t="n">
-        <v>0.512293619670203</v>
+        <v>0.5122912715463731</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5114767707650669</v>
+        <v>0.5114767707653582</v>
       </c>
     </row>
     <row r="10">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.0183005946729256</v>
+        <v>-0.01830059467297169</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.01865545621593882</v>
+        <v>-0.01853357407744222</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01338558166972412</v>
+        <v>-0.01338558167183207</v>
       </c>
     </row>
   </sheetData>

--- a/TP4/coeficientes_comparados.xlsx
+++ b/TP4/coeficientes_comparados.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.2674712948078108</v>
+        <v>-0.267471294807786</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2677980367466836</v>
+        <v>-0.2679994045568237</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2644778012909151</v>
+        <v>-0.2644778012912836</v>
       </c>
     </row>
     <row r="3">
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.3357418794624388</v>
+        <v>-0.3357418794625224</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.317248377097728</v>
+        <v>-0.3271063040247893</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1916526710523312</v>
+        <v>-0.1916526710678866</v>
       </c>
     </row>
     <row r="4">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2987889723351313</v>
+        <v>0.2987889723352566</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2820729688634421</v>
+        <v>0.291646649069005</v>
       </c>
       <c r="E4" t="n">
-        <v>0.156618198693959</v>
+        <v>0.1566181987043967</v>
       </c>
     </row>
     <row r="5">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.2377976524469907</v>
+        <v>-0.2377976524470184</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2379799976013406</v>
+        <v>-0.2386182152075327</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2337632746645101</v>
+        <v>-0.2337632746595569</v>
       </c>
     </row>
     <row r="6">
@@ -536,13 +536,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6783330399313007</v>
+        <v>0.6783330399313084</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6792264030024556</v>
+        <v>0.6791362379886846</v>
       </c>
       <c r="E6" t="n">
-        <v>0.677548417276601</v>
+        <v>0.6775484172732671</v>
       </c>
     </row>
     <row r="7">
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2402097828474914</v>
+        <v>0.2402097828475757</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2416847748220056</v>
+        <v>0.2414959230495421</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2370293383284964</v>
+        <v>0.2370293383297625</v>
       </c>
     </row>
     <row r="8">
@@ -574,13 +574,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03635745172597279</v>
+        <v>0.03635745172598552</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03731824384443799</v>
+        <v>0.03721878147491221</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03752849576228024</v>
+        <v>0.03752849576043522</v>
       </c>
     </row>
     <row r="9">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.5118058638438978</v>
+        <v>0.5118058638439145</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5122912715463731</v>
+        <v>0.5122335322549993</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5114767707653582</v>
+        <v>0.5114767707646297</v>
       </c>
     </row>
     <row r="10">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.01830059467297169</v>
+        <v>-0.01830059467295767</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.01853357407744222</v>
+        <v>-0.01922278424026939</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01338558167183207</v>
+        <v>-0.01338558166906005</v>
       </c>
     </row>
   </sheetData>
